--- a/data/trans_camb/IP2005-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 4,69</t>
+          <t>-7,07; 4,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 8,87</t>
+          <t>-2,78; 9,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 5,58</t>
+          <t>-7,54; 5,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,5</t>
+          <t>-8,46; 3,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,2</t>
+          <t>-7,39; 4,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,14</t>
+          <t>-8,09; 4,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,71</t>
+          <t>-5,91; 2,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 4,69</t>
+          <t>-3,21; 4,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,92</t>
+          <t>-5,7; 2,87</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 5,37</t>
+          <t>-7,67; 5,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 10,26</t>
+          <t>-3,05; 10,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 6,37</t>
+          <t>-8,1; 6,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 3,93</t>
+          <t>-9,08; 3,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 4,65</t>
+          <t>-8,14; 4,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 5,73</t>
+          <t>-8,66; 5,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 3,04</t>
+          <t>-6,31; 2,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 5,24</t>
+          <t>-3,47; 5,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 4,3</t>
+          <t>-6,15; 3,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 7,72</t>
+          <t>-2,55; 7,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,14</t>
+          <t>1,2; 11,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,5</t>
+          <t>0,94; 10,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,27</t>
+          <t>1,65; 12,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,31</t>
+          <t>3,94; 14,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 11,19</t>
+          <t>0,58; 12,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,48</t>
+          <t>0,98; 8,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 11,17</t>
+          <t>4,63; 11,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,67</t>
+          <t>1,89; 9,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 9,36</t>
+          <t>-2,84; 9,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 13,21</t>
+          <t>1,35; 13,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,05</t>
+          <t>1,03; 12,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 15,21</t>
+          <t>2,03; 16,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 18,04</t>
+          <t>4,56; 18,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 14,09</t>
+          <t>0,61; 15,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 10,18</t>
+          <t>1,12; 10,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,46</t>
+          <t>5,23; 13,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,68</t>
+          <t>2,1; 11,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 5,72</t>
+          <t>-5,57; 5,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 9,63</t>
+          <t>-0,32; 8,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 6,06</t>
+          <t>-6,01; 5,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 2,31</t>
+          <t>-7,34; 2,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 2,39</t>
+          <t>-8,35; 1,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 0,41</t>
+          <t>-9,82; 0,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,53</t>
+          <t>-4,86; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,74</t>
+          <t>-3,32; 3,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 1,29</t>
+          <t>-6,21; 1,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,58</t>
+          <t>-6,01; 6,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 11,19</t>
+          <t>-0,33; 10,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,96</t>
+          <t>-6,43; 6,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 2,52</t>
+          <t>-7,65; 2,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 2,54</t>
+          <t>-8,81; 1,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 0,42</t>
+          <t>-10,5; 0,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 2,83</t>
+          <t>-5,19; 2,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,19</t>
+          <t>-3,55; 4,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,41</t>
+          <t>-6,68; 1,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 8,11</t>
+          <t>-2,3; 8,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 8,32</t>
+          <t>-1,12; 9,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -3,75</t>
+          <t>-16,44; -3,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 7,98</t>
+          <t>-1,56; 7,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 6,53</t>
+          <t>-3,16; 6,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,86; -0,39</t>
+          <t>-12,34; 0,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,69</t>
+          <t>-0,14; 6,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 6,13</t>
+          <t>-0,63; 6,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,23; -3,23</t>
+          <t>-13,01; -3,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 9,56</t>
+          <t>-2,49; 9,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 9,74</t>
+          <t>-1,1; 11,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -4,15</t>
+          <t>-18,14; -4,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 9,38</t>
+          <t>-1,61; 8,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 7,54</t>
+          <t>-3,38; 7,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -0,48</t>
+          <t>-13,56; 0,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 7,72</t>
+          <t>-0,15; 7,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 7,01</t>
+          <t>-0,65; 7,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -3,72</t>
+          <t>-14,31; -4,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,21</t>
+          <t>-1,24; 4,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,89</t>
+          <t>1,89; 7,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,73</t>
+          <t>-4,18; 2,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,65</t>
+          <t>-0,52; 4,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,01</t>
+          <t>-0,46; 4,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,14</t>
+          <t>-3,89; 2,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,53</t>
+          <t>-0,16; 3,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,18</t>
+          <t>1,47; 5,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,14</t>
+          <t>-3,15; 1,25</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,85</t>
+          <t>-1,37; 4,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,9</t>
+          <t>2,07; 8,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 1,97</t>
+          <t>-4,64; 2,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,34</t>
+          <t>-0,62; 5,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,77</t>
+          <t>-0,52; 5,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,44</t>
+          <t>-4,33; 2,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,99</t>
+          <t>-0,18; 4,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,94</t>
+          <t>1,64; 6,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,29</t>
+          <t>-3,55; 1,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 4,9</t>
+          <t>-7,37; 5,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 9,12</t>
+          <t>-2,62; 8,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 5,49</t>
+          <t>-7,31; 5,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 3,37</t>
+          <t>-7,82; 3,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,37</t>
+          <t>-6,99; 4,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 4,94</t>
+          <t>-8,27; 4,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 2,35</t>
+          <t>-6,28; 2,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 4,55</t>
+          <t>-3,32; 4,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 2,87</t>
+          <t>-5,39; 3,29</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 5,52</t>
+          <t>-7,9; 6,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 10,56</t>
+          <t>-2,8; 9,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 6,19</t>
+          <t>-8,03; 5,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 3,83</t>
+          <t>-8,41; 4,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 4,97</t>
+          <t>-7,34; 5,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 5,62</t>
+          <t>-8,97; 5,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 2,66</t>
+          <t>-6,75; 2,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,11</t>
+          <t>-3,57; 5,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,18</t>
+          <t>-5,85; 3,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 7,65</t>
+          <t>-2,15; 7,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,03</t>
+          <t>1,22; 11,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,76</t>
+          <t>1,17; 11,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 12,73</t>
+          <t>1,45; 11,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 14,86</t>
+          <t>4,66; 14,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 12,17</t>
+          <t>0,39; 12,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,72</t>
+          <t>0,93; 8,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,49</t>
+          <t>4,33; 11,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,74</t>
+          <t>2,05; 9,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 9,11</t>
+          <t>-2,3; 9,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,32</t>
+          <t>1,38; 13,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,86</t>
+          <t>1,3; 13,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 16,06</t>
+          <t>1,69; 14,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 18,55</t>
+          <t>5,41; 18,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 15,0</t>
+          <t>0,46; 15,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,6</t>
+          <t>1,12; 10,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,75</t>
+          <t>5,01; 13,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,81</t>
+          <t>2,4; 11,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 5,87</t>
+          <t>-5,31; 5,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 8,9</t>
+          <t>-0,46; 9,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 5,88</t>
+          <t>-6,43; 6,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 2,65</t>
+          <t>-7,14; 2,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 1,81</t>
+          <t>-8,88; 2,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 0,45</t>
+          <t>-10,03; 0,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,46</t>
+          <t>-4,69; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,97</t>
+          <t>-3,13; 4,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 1,45</t>
+          <t>-6,73; 1,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 6,67</t>
+          <t>-5,79; 6,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 10,27</t>
+          <t>-0,49; 10,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,75</t>
+          <t>-6,95; 6,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 2,88</t>
+          <t>-7,48; 3,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 1,98</t>
+          <t>-9,35; 2,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 0,45</t>
+          <t>-10,49; 0,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 2,71</t>
+          <t>-5,04; 2,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,34</t>
+          <t>-3,35; 4,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,69</t>
+          <t>-7,24; 2,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,05</t>
+          <t>-2,01; 8,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 9,26</t>
+          <t>-1,11; 8,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,44; -3,65</t>
+          <t>-16,86; -3,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 7,75</t>
+          <t>-1,92; 7,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 6,58</t>
+          <t>-3,24; 6,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 0,17</t>
+          <t>-12,3; 0,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 6,68</t>
+          <t>-0,51; 6,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,27</t>
+          <t>-0,89; 6,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -3,62</t>
+          <t>-12,39; -2,96</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,45</t>
+          <t>-2,14; 9,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 11,04</t>
+          <t>-1,17; 10,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,14; -4,34</t>
+          <t>-18,48; -3,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 8,91</t>
+          <t>-2,06; 8,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 7,57</t>
+          <t>-3,49; 7,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 0,19</t>
+          <t>-13,47; -0,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,71</t>
+          <t>-0,56; 7,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,31</t>
+          <t>-0,97; 7,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -4,14</t>
+          <t>-13,78; -3,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,18</t>
+          <t>-1,18; 4,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,08</t>
+          <t>1,95; 7,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,23</t>
+          <t>-3,98; 2,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,81</t>
+          <t>-0,38; 4,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,84</t>
+          <t>-0,5; 5,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,14</t>
+          <t>-3,93; 2,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,62</t>
+          <t>-0,06; 3,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,31</t>
+          <t>1,53; 5,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,25</t>
+          <t>-2,92; 1,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,76</t>
+          <t>-1,31; 4,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,16</t>
+          <t>2,17; 8,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,56</t>
+          <t>-4,41; 2,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,52</t>
+          <t>-0,42; 5,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,51</t>
+          <t>-0,56; 5,87</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,44</t>
+          <t>-4,34; 2,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,12</t>
+          <t>-0,07; 4,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,03</t>
+          <t>1,71; 6,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,42</t>
+          <t>-3,25; 1,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,03</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-1,21</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 5,45</t>
+          <t>-7,7; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 8,23</t>
+          <t>-7,23; 4,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 5,04</t>
+          <t>-6,88; 4,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 3,84</t>
+          <t>-7,15; 4,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 4,43</t>
+          <t>-3,04; 8,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 4,87</t>
+          <t>-8,07; 5,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,46</t>
+          <t>-5,75; 2,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 4,6</t>
+          <t>-3,33; 4,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,29</t>
+          <t>-5,4; 3,78</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-2,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-1,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-1,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-1,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,19%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,46%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>-1,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1,24%</t>
+          <t>-1,33%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 6,36</t>
+          <t>-8,28; 3,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 9,36</t>
+          <t>-7,9; 4,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 5,76</t>
+          <t>-7,4; 5,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 4,31</t>
+          <t>-7,81; 5,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 5,01</t>
+          <t>-3,3; 10,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 5,53</t>
+          <t>-8,63; 6,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 2,79</t>
+          <t>-6,28; 3,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 5,13</t>
+          <t>-3,56; 5,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 3,68</t>
+          <t>-5,95; 4,21</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,39</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,34</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>6,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,81</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,39</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>6,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 7,76</t>
+          <t>1,72; 12,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,03</t>
+          <t>4,4; 14,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,41</t>
+          <t>0,47; 11,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 11,57</t>
+          <t>-2,62; 7,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 14,81</t>
+          <t>1,22; 11,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 12,13</t>
+          <t>1,06; 11,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,54</t>
+          <t>1,43; 8,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,47</t>
+          <t>4,13; 11,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,46</t>
+          <t>2,22; 9,63</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,11%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6,92%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 9,4</t>
+          <t>2,04; 15,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,22</t>
+          <t>5,22; 18,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 13,55</t>
+          <t>0,56; 14,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 14,56</t>
+          <t>-2,85; 9,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 18,75</t>
+          <t>1,34; 13,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 15,2</t>
+          <t>1,19; 13,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,53</t>
+          <t>1,65; 10,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 13,95</t>
+          <t>4,68; 13,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 11,51</t>
+          <t>2,61; 11,69</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,01</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,61</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>4,18</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-3,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 5,77</t>
+          <t>-6,91; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 9,27</t>
+          <t>-8,18; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,0</t>
+          <t>-10,24; 0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,72</t>
+          <t>-5,98; 5,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 2,13</t>
+          <t>-0,37; 9,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 0,51</t>
+          <t>-8,14; 3,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,68</t>
+          <t>-4,9; 2,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 4,18</t>
+          <t>-3,13; 3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 1,83</t>
+          <t>-7,48; 0,25</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-2,31%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-3,23%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-4,95%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,04%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-0,58%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,31%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3,23%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,77%</t>
+          <t>-2,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,76%</t>
+          <t>-3,72%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 6,62</t>
+          <t>-7,36; 2,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 10,83</t>
+          <t>-8,75; 2,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 6,92</t>
+          <t>-10,89; 0,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 3,05</t>
+          <t>-6,43; 6,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 2,48</t>
+          <t>-0,37; 11,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 0,63</t>
+          <t>-8,73; 4,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,96</t>
+          <t>-5,23; 2,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 4,65</t>
+          <t>-3,38; 4,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 2,01</t>
+          <t>-8,05; 0,3</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,59</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,06</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,78</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,91</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,04</t>
+          <t>-10,14</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,89</t>
+          <t>-8,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 8,49</t>
+          <t>-1,55; 7,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,64</t>
+          <t>-3,46; 6,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -3,36</t>
+          <t>-13,22; -0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,73</t>
+          <t>-2,15; 8,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 6,54</t>
+          <t>-1,96; 8,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 0,01</t>
+          <t>-17,56; -3,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,77</t>
+          <t>-0,38; 6,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 6,12</t>
+          <t>-0,94; 6,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -2,96</t>
+          <t>-12,49; -3,62</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-7,05%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,26%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-11,18%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-6,72%</t>
+          <t>-11,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,83%</t>
+          <t>-9,21%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 9,87</t>
+          <t>-1,6; 9,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 10,19</t>
+          <t>-3,71; 7,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,48; -3,78</t>
+          <t>-14,4; -0,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 8,92</t>
+          <t>-2,27; 9,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 7,62</t>
+          <t>-2,11; 9,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,47; -0,25</t>
+          <t>-19,42; -4,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 7,74</t>
+          <t>-0,4; 7,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 7,0</t>
+          <t>-1,0; 7,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -3,42</t>
+          <t>-13,87; -4,16</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,08</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>4,39</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,09</t>
+          <t>-0,7; 4,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,03</t>
+          <t>-0,4; 5,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,17</t>
+          <t>-3,88; 2,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,76</t>
+          <t>-1,26; 4,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,09</t>
+          <t>1,69; 6,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,19</t>
+          <t>-4,88; 1,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,77</t>
+          <t>-0,23; 3,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,27</t>
+          <t>1,42; 5,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,37</t>
+          <t>-3,3; 0,73</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-1,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-1,15%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,93%</t>
+          <t>-1,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,03%</t>
+          <t>-1,41%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,66</t>
+          <t>-0,77; 5,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,08</t>
+          <t>-0,45; 5,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,46</t>
+          <t>-4,31; 2,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,46</t>
+          <t>-1,4; 4,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,87</t>
+          <t>1,88; 7,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,52</t>
+          <t>-5,4; 1,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,31</t>
+          <t>-0,26; 3,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,01</t>
+          <t>1,58; 5,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,56</t>
+          <t>-3,66; 0,83</t>
         </is>
       </c>
     </row>
